--- a/artfynd/A 42576-2022 artfynd.xlsx
+++ b/artfynd/A 42576-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118676853</v>
       </c>
       <c r="B2" t="n">
-        <v>97867</v>
+        <v>97874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 42576-2022 artfynd.xlsx
+++ b/artfynd/A 42576-2022 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819476</v>
+        <v>119819475</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489022</v>
+        <v>489029</v>
       </c>
       <c r="R3" t="n">
-        <v>6862488</v>
+        <v>6862246</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819474</v>
+        <v>119819476</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489127</v>
+        <v>489022</v>
       </c>
       <c r="R4" t="n">
-        <v>6862156</v>
+        <v>6862488</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819475</v>
+        <v>119819469</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489029</v>
+        <v>488865</v>
       </c>
       <c r="R5" t="n">
-        <v>6862246</v>
+        <v>6862178</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819469</v>
+        <v>119819474</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488865</v>
+        <v>489127</v>
       </c>
       <c r="R6" t="n">
-        <v>6862178</v>
+        <v>6862156</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>

--- a/artfynd/A 42576-2022 artfynd.xlsx
+++ b/artfynd/A 42576-2022 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819475</v>
+        <v>119819474</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489029</v>
+        <v>489127</v>
       </c>
       <c r="R3" t="n">
-        <v>6862246</v>
+        <v>6862156</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819469</v>
+        <v>119819475</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488865</v>
+        <v>489029</v>
       </c>
       <c r="R5" t="n">
-        <v>6862178</v>
+        <v>6862246</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819474</v>
+        <v>119819469</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489127</v>
+        <v>488865</v>
       </c>
       <c r="R6" t="n">
-        <v>6862156</v>
+        <v>6862178</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>

--- a/artfynd/A 42576-2022 artfynd.xlsx
+++ b/artfynd/A 42576-2022 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819474</v>
+        <v>119819475</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489127</v>
+        <v>489029</v>
       </c>
       <c r="R3" t="n">
-        <v>6862156</v>
+        <v>6862246</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819476</v>
+        <v>119819474</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489022</v>
+        <v>489127</v>
       </c>
       <c r="R4" t="n">
-        <v>6862488</v>
+        <v>6862156</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819475</v>
+        <v>119819476</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489029</v>
+        <v>489022</v>
       </c>
       <c r="R5" t="n">
-        <v>6862246</v>
+        <v>6862488</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 42576-2022 artfynd.xlsx
+++ b/artfynd/A 42576-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>119819475</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819474</v>
+        <v>119819476</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489127</v>
+        <v>489022</v>
       </c>
       <c r="R4" t="n">
-        <v>6862156</v>
+        <v>6862488</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819476</v>
+        <v>119819469</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>91870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489022</v>
+        <v>488865</v>
       </c>
       <c r="R5" t="n">
-        <v>6862488</v>
+        <v>6862178</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819469</v>
+        <v>119819474</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>97953</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1135,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488865</v>
+        <v>489127</v>
       </c>
       <c r="R6" t="n">
-        <v>6862178</v>
+        <v>6862156</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>

--- a/artfynd/A 42576-2022 artfynd.xlsx
+++ b/artfynd/A 42576-2022 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819475</v>
+        <v>119819476</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489029</v>
+        <v>489022</v>
       </c>
       <c r="R3" t="n">
-        <v>6862246</v>
+        <v>6862488</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819476</v>
+        <v>119819475</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489022</v>
+        <v>489029</v>
       </c>
       <c r="R4" t="n">
-        <v>6862488</v>
+        <v>6862246</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 42576-2022 artfynd.xlsx
+++ b/artfynd/A 42576-2022 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819475</v>
+        <v>119819469</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>91870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489029</v>
+        <v>488865</v>
       </c>
       <c r="R4" t="n">
-        <v>6862246</v>
+        <v>6862178</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819469</v>
+        <v>119819475</v>
       </c>
       <c r="B5" t="n">
-        <v>91870</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488865</v>
+        <v>489029</v>
       </c>
       <c r="R5" t="n">
-        <v>6862178</v>
+        <v>6862246</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 42576-2022 artfynd.xlsx
+++ b/artfynd/A 42576-2022 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819469</v>
+        <v>119819475</v>
       </c>
       <c r="B4" t="n">
-        <v>91870</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488865</v>
+        <v>489029</v>
       </c>
       <c r="R4" t="n">
-        <v>6862178</v>
+        <v>6862246</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119819475</v>
+        <v>119819469</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>91870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1020,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489029</v>
+        <v>488865</v>
       </c>
       <c r="R5" t="n">
-        <v>6862246</v>
+        <v>6862178</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
